--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -1303,7 +1303,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -630,13 +630,13 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>Observation.category:vitalSigns</t>
-  </si>
-  <si>
-    <t>vitalSigns</t>
-  </si>
-  <si>
-    <t>Observation.category:vitalSigns.id</t>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>Observation.category:first.id</t>
   </si>
   <si>
     <t>Observation.category.id</t>
@@ -658,7 +658,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.category:vitalSigns.extension</t>
+    <t>Observation.category:first.extension</t>
   </si>
   <si>
     <t>Observation.category.extension</t>
@@ -677,7 +677,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Observation.category:vitalSigns.coding</t>
+    <t>Observation.category:first.coding</t>
   </si>
   <si>
     <t>Observation.category.coding</t>
@@ -708,19 +708,19 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Observation.category:vitalSigns.coding.id</t>
+    <t>Observation.category:first.coding.id</t>
   </si>
   <si>
     <t>Observation.category.coding.id</t>
   </si>
   <si>
-    <t>Observation.category:vitalSigns.coding.extension</t>
+    <t>Observation.category:first.coding.extension</t>
   </si>
   <si>
     <t>Observation.category.coding.extension</t>
   </si>
   <si>
-    <t>Observation.category:vitalSigns.coding.system</t>
+    <t>Observation.category:first.coding.system</t>
   </si>
   <si>
     <t>Observation.category.coding.system</t>
@@ -750,7 +750,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Observation.category:vitalSigns.coding.version</t>
+    <t>Observation.category:first.coding.version</t>
   </si>
   <si>
     <t>Observation.category.coding.version</t>
@@ -774,7 +774,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Observation.category:vitalSigns.coding.code</t>
+    <t>Observation.category:first.coding.code</t>
   </si>
   <si>
     <t>Observation.category.coding.code</t>
@@ -801,7 +801,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Observation.category:vitalSigns.coding.display</t>
+    <t>Observation.category:first.coding.display</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -825,7 +825,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Observation.category:vitalSigns.coding.userSelected</t>
+    <t>Observation.category:first.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.category.coding.userSelected</t>
@@ -856,7 +856,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Observation.category:vitalSigns.text</t>
+    <t>Observation.category:first.text</t>
   </si>
   <si>
     <t>Observation.category.text</t>
@@ -883,10 +883,10 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>Observation.category:vitalSignCategory</t>
-  </si>
-  <si>
-    <t>vitalSignCategory</t>
+    <t>Observation.category:second</t>
+  </si>
+  <si>
+    <t>second</t>
   </si>
   <si>
     <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１．バイタルサイン・基本情報、中分類１．バイタルサインの「焦点」</t>
@@ -895,40 +895,40 @@
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationVitalSignsCategory_VS</t>
   </si>
   <si>
-    <t>Observation.category:vitalSignCategory.id</t>
-  </si>
-  <si>
-    <t>Observation.category:vitalSignCategory.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:vitalSignCategory.coding</t>
-  </si>
-  <si>
-    <t>Observation.category:vitalSignCategory.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category:vitalSignCategory.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:vitalSignCategory.coding.system</t>
+    <t>Observation.category:second.id</t>
+  </si>
+  <si>
+    <t>Observation.category:second.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.system</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationVitalSignsCategory_CS</t>
   </si>
   <si>
-    <t>Observation.category:vitalSignCategory.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category:vitalSignCategory.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.category:vitalSignCategory.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.category:vitalSignCategory.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.category:vitalSignCategory.text</t>
+    <t>Observation.category:second.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.category:second.text</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1961,9 +1961,9 @@
   <dimension ref="A1:AP75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.0703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.2890625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.36328125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -1366,7 +1366,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2912" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="530">
   <si>
     <t>Property</t>
   </si>
@@ -614,7 +614,10 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -634,6 +637,18 @@
   </si>
   <si>
     <t>first</t>
+  </si>
+  <si>
+    <t>検査の第1カテゴリはJP_SimpleObservationCategory_VSから値を指定する。</t>
+  </si>
+  <si>
+    <t>行われている一般的なタイプの観測を分類するコード。 / A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -3761,22 +3776,24 @@
       <c r="X15" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y15" s="2"/>
+      <c r="Y15" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3803,10 +3820,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3814,13 +3831,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -3830,7 +3847,7 @@
         <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -3845,13 +3862,13 @@
         <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>191</v>
@@ -3883,7 +3900,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3925,10 +3942,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -3936,10 +3953,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3962,13 +3979,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4019,7 +4036,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4043,7 +4060,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4054,10 +4071,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4086,7 +4103,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4127,19 +4144,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4163,7 +4180,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4174,10 +4191,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4200,19 +4217,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4261,7 +4278,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4282,10 +4299,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4296,10 +4313,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4322,13 +4339,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4379,7 +4396,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4403,7 +4420,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4414,10 +4431,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4446,7 +4463,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4487,19 +4504,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4523,7 +4540,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4534,10 +4551,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4563,23 +4580,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4621,7 +4638,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4642,10 +4659,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4656,10 +4673,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4682,16 +4699,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4741,7 +4758,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4762,10 +4779,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4776,10 +4793,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4805,21 +4822,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4861,7 +4878,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4882,10 +4899,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4896,10 +4913,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4922,17 +4939,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4981,7 +4998,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5002,10 +5019,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5016,10 +5033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5042,19 +5059,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5103,7 +5120,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5124,10 +5141,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5138,10 +5155,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5164,19 +5181,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5225,7 +5242,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5246,10 +5263,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5260,13 +5277,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5297,7 +5314,7 @@
         <v>189</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>191</v>
@@ -5329,7 +5346,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5371,10 +5388,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5382,10 +5399,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5408,13 +5425,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5465,7 +5482,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5489,7 +5506,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5500,10 +5517,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5532,7 +5549,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5573,19 +5590,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5609,7 +5626,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5620,10 +5637,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5646,19 +5663,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5707,7 +5724,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5728,10 +5745,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5742,10 +5759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5768,13 +5785,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5825,7 +5842,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5849,7 +5866,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5860,10 +5877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5892,7 +5909,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -5933,19 +5950,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5969,7 +5986,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -5980,10 +5997,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6009,23 +6026,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6067,7 +6084,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6088,10 +6105,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6102,10 +6119,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6128,16 +6145,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6187,7 +6204,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6208,10 +6225,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6222,10 +6239,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6251,14 +6268,14 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6307,7 +6324,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6328,10 +6345,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6342,10 +6359,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6368,17 +6385,17 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6427,7 +6444,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6448,10 +6465,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6462,10 +6479,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6488,19 +6505,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6549,7 +6566,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6570,10 +6587,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6584,10 +6601,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6610,19 +6627,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6671,7 +6688,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6692,10 +6709,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6706,14 +6723,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6735,16 +6752,16 @@
         <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6773,25 +6790,25 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -6806,30 +6823,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6852,19 +6869,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6913,7 +6930,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6928,19 +6945,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -6948,10 +6965,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6974,16 +6991,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7033,7 +7050,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7054,13 +7071,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7068,14 +7085,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7094,19 +7111,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7155,7 +7172,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7170,19 +7187,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7190,14 +7207,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7216,19 +7233,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7277,7 +7294,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7292,19 +7309,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7312,10 +7329,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7338,16 +7355,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7397,7 +7414,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7418,13 +7435,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7432,10 +7449,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7458,19 +7475,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7519,7 +7536,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7534,19 +7551,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7554,10 +7571,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7580,19 +7597,19 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7641,7 +7658,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7650,7 +7667,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7659,27 +7676,27 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7705,16 +7722,16 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7739,31 +7756,31 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7772,7 +7789,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7787,7 +7804,7 @@
         <v>137</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7798,14 +7815,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7827,16 +7844,16 @@
         <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7861,31 +7878,31 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7903,27 +7920,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7946,19 +7963,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8007,7 +8024,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8028,10 +8045,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8042,10 +8059,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8071,13 +8088,13 @@
         <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8103,31 +8120,31 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="Z51" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8145,27 +8162,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8191,16 +8208,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8225,31 +8242,31 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="Z52" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8270,10 +8287,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8284,10 +8301,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8310,16 +8327,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8369,7 +8386,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8387,27 +8404,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8430,16 +8447,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8489,7 +8506,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8507,27 +8524,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8550,19 +8567,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8611,7 +8628,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8623,7 +8640,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8632,10 +8649,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8646,10 +8663,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8672,13 +8689,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8729,7 +8746,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8753,7 +8770,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8764,10 +8781,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8796,7 +8813,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -8849,7 +8866,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8873,7 +8890,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8884,14 +8901,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8913,10 +8930,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -8971,7 +8988,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9006,10 +9023,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9032,13 +9049,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9089,7 +9106,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9098,7 +9115,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9110,10 +9127,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9124,10 +9141,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9150,13 +9167,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9207,7 +9224,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9216,7 +9233,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9228,10 +9245,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9242,10 +9259,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9271,16 +9288,16 @@
         <v>188</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9308,28 +9325,28 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9347,13 +9364,13 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9364,10 +9381,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9393,16 +9410,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9427,31 +9444,31 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9469,13 +9486,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9486,10 +9503,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9512,17 +9529,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9571,7 +9588,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9595,7 +9612,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9606,10 +9623,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9632,13 +9649,13 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9689,7 +9706,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9710,10 +9727,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9724,10 +9741,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9750,16 +9767,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9809,7 +9826,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9830,10 +9847,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9844,10 +9861,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9870,16 +9887,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9929,7 +9946,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9950,10 +9967,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -9964,10 +9981,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9990,19 +10007,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10051,7 +10068,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10072,10 +10089,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10086,10 +10103,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10112,13 +10129,13 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10169,7 +10186,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10193,7 +10210,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10204,10 +10221,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10236,7 +10253,7 @@
         <v>141</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>143</v>
@@ -10289,7 +10306,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10313,7 +10330,7 @@
         <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10324,14 +10341,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10353,10 +10370,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10411,7 +10428,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10446,10 +10463,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10475,16 +10492,16 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10513,7 +10530,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10531,7 +10548,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10549,16 +10566,16 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -10566,10 +10583,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10592,19 +10609,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10653,7 +10670,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10671,27 +10688,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10717,16 +10734,16 @@
         <v>188</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10751,13 +10768,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10775,7 +10792,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10784,7 +10801,7 @@
         <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>106</v>
@@ -10799,7 +10816,7 @@
         <v>137</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10810,14 +10827,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10839,16 +10856,16 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10873,13 +10890,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10897,7 +10914,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10915,27 +10932,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10961,16 +10978,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11019,7 +11036,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11040,10 +11057,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2912" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -1273,10 +1273,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -8122,11 +8119,9 @@
       <c r="X51" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Y51" s="2"/>
+      <c r="Z51" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8162,27 +8157,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>409</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8208,16 +8203,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8245,11 +8240,11 @@
         <v>403</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>415</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8266,7 +8261,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8287,10 +8282,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8301,10 +8296,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8327,16 +8322,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8386,7 +8381,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8404,27 +8399,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>425</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8447,16 +8442,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8506,7 +8501,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8524,27 +8519,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>433</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8567,19 +8562,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8628,7 +8623,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8640,19 +8635,19 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8663,10 +8658,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8781,10 +8776,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8901,14 +8896,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8930,10 +8925,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -8988,7 +8983,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9023,10 +9018,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9049,13 +9044,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9106,7 +9101,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9115,7 +9110,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9127,10 +9122,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9141,10 +9136,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9167,13 +9162,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9224,7 +9219,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9233,7 +9228,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9245,10 +9240,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9259,10 +9254,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9288,16 +9283,16 @@
         <v>188</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9325,11 +9320,11 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>466</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9346,7 +9341,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9364,10 +9359,10 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>391</v>
@@ -9381,10 +9376,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9410,16 +9405,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9447,11 +9442,11 @@
         <v>403</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>475</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9468,7 +9463,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9486,10 +9481,10 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>391</v>
@@ -9503,10 +9498,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9529,17 +9524,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9588,7 +9583,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9612,7 +9607,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9623,10 +9618,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9652,10 +9647,10 @@
         <v>206</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9706,7 +9701,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9727,10 +9722,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9741,10 +9736,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9767,16 +9762,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9826,7 +9821,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9847,10 +9842,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9861,10 +9856,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9887,16 +9882,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9946,7 +9941,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9967,10 +9962,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -9981,10 +9976,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10007,19 +10002,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10068,7 +10063,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10089,10 +10084,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10103,10 +10098,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10221,10 +10216,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10341,14 +10336,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10370,10 +10365,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10428,7 +10423,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10463,10 +10458,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10492,13 +10487,13 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>305</v>
@@ -10548,7 +10543,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10566,7 +10561,7 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>309</v>
@@ -10583,10 +10578,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10612,13 +10607,13 @@
         <v>364</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>367</v>
@@ -10670,7 +10665,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10688,7 +10683,7 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>370</v>
@@ -10705,10 +10700,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10734,13 +10729,13 @@
         <v>188</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>376</v>
@@ -10792,7 +10787,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10827,10 +10822,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10856,16 +10851,16 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10914,7 +10909,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10949,10 +10944,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10978,16 +10973,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11036,7 +11031,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11057,10 +11052,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1189,7 +1189,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1379,7 +1379,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1635,7 +1635,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -1997,7 +1997,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="65.90625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -1450,7 +1450,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -1973,15 +1973,15 @@
   <dimension ref="A1:AP75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.2890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.54296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1992,28 +1992,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.90625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.5" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2912" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="530">
   <si>
     <t>Property</t>
   </si>
@@ -1273,7 +1273,10 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -8119,9 +8122,11 @@
       <c r="X51" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="Y51" s="2"/>
+      <c r="Y51" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8157,27 +8162,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8203,16 +8208,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8240,10 +8245,10 @@
         <v>403</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8261,7 +8266,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8282,10 +8287,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8296,10 +8301,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8322,16 +8327,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8381,7 +8386,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8399,27 +8404,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8442,16 +8447,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8501,7 +8506,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8519,27 +8524,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8562,19 +8567,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8623,7 +8628,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8635,7 +8640,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8644,10 +8649,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8658,10 +8663,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8776,10 +8781,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8896,14 +8901,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8925,10 +8930,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -8983,7 +8988,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9018,10 +9023,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9044,13 +9049,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9101,7 +9106,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9110,7 +9115,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9122,10 +9127,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9136,10 +9141,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9162,13 +9167,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9219,7 +9224,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9228,7 +9233,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9240,10 +9245,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9254,10 +9259,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9283,16 +9288,16 @@
         <v>188</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9320,10 +9325,10 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9341,7 +9346,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9359,10 +9364,10 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>391</v>
@@ -9376,10 +9381,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9405,16 +9410,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9442,10 +9447,10 @@
         <v>403</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9463,7 +9468,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9481,10 +9486,10 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>391</v>
@@ -9498,10 +9503,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9524,17 +9529,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9583,7 +9588,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9607,7 +9612,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9618,10 +9623,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9647,10 +9652,10 @@
         <v>206</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9701,7 +9706,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9722,10 +9727,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9736,10 +9741,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9762,16 +9767,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9821,7 +9826,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9842,10 +9847,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9856,10 +9861,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9882,16 +9887,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9941,7 +9946,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9962,10 +9967,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -9976,10 +9981,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10002,19 +10007,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10063,7 +10068,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10084,10 +10089,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10098,10 +10103,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10216,10 +10221,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10336,14 +10341,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10365,10 +10370,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10423,7 +10428,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10458,10 +10463,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10487,13 +10492,13 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>305</v>
@@ -10543,7 +10548,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10561,7 +10566,7 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>309</v>
@@ -10578,10 +10583,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10607,13 +10612,13 @@
         <v>364</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>367</v>
@@ -10665,7 +10670,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10683,7 +10688,7 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>370</v>
@@ -10700,10 +10705,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10729,13 +10734,13 @@
         <v>188</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>376</v>
@@ -10787,7 +10792,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10822,10 +10827,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10851,16 +10856,16 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10909,7 +10914,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10944,10 +10949,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10973,16 +10978,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11031,7 +11036,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11052,10 +11057,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -617,7 +617,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1014,7 +1014,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1192,7 +1192,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1221,7 +1221,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1276,7 +1276,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1306,7 +1306,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1343,7 +1343,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1418,7 +1418,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1468,7 +1468,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1501,7 +1501,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -620,7 +620,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="519">
   <si>
     <t>Property</t>
   </si>
@@ -907,43 +907,14 @@
     <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１．バイタルサイン・基本情報、中分類１．バイタルサインの「焦点」</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationVitalSignsCategory_CS"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationVitalSignsCategory_VS</t>
-  </si>
-  <si>
-    <t>Observation.category:second.id</t>
-  </si>
-  <si>
-    <t>Observation.category:second.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.system</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationVitalSignsCategory_CS</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.category:second.text</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1973,10 +1944,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP75"/>
+  <dimension ref="A1:AP64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.54296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -5327,7 +5298,7 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>83</v>
@@ -5346,7 +5317,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5399,18 +5370,18 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>205</v>
+        <v>290</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>94</v>
@@ -5422,19 +5393,23 @@
         <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
       </c>
@@ -5458,13 +5433,11 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
@@ -5482,10 +5455,10 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>209</v>
+        <v>290</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>94</v>
@@ -5494,44 +5467,44 @@
         <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>83</v>
+        <v>298</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>210</v>
+        <v>299</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>83</v>
+        <v>301</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>212</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>83</v>
@@ -5540,21 +5513,23 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>140</v>
+        <v>303</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>141</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>213</v>
+        <v>304</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
       </c>
@@ -5590,46 +5565,46 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>216</v>
+        <v>302</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>83</v>
+        <v>307</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>83</v>
+        <v>308</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>210</v>
+        <v>309</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
@@ -5637,10 +5612,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>218</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5663,20 +5638,18 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>219</v>
+        <v>312</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>220</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>221</v>
+        <v>313</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5724,7 +5697,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>224</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5745,13 +5718,13 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>225</v>
+        <v>298</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>226</v>
+        <v>315</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
@@ -5759,14 +5732,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>228</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5782,19 +5755,23 @@
         <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>207</v>
+        <v>319</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
@@ -5842,7 +5819,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>209</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5854,22 +5831,22 @@
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>210</v>
+        <v>324</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5877,21 +5854,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>230</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>139</v>
+        <v>327</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5900,21 +5877,23 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>140</v>
+        <v>328</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>141</v>
+        <v>329</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>213</v>
+        <v>329</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
@@ -5950,46 +5929,46 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>216</v>
+        <v>326</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>210</v>
+        <v>334</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>83</v>
+        <v>335</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -5997,10 +5976,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>232</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6023,26 +6002,24 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>108</v>
+        <v>337</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>233</v>
+        <v>338</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>234</v>
+        <v>338</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6084,7 +6061,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>238</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6105,13 +6082,13 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>239</v>
+        <v>340</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>240</v>
+        <v>341</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>83</v>
+        <v>342</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
@@ -6119,10 +6096,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>242</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6133,7 +6110,7 @@
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6145,18 +6122,20 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>206</v>
+        <v>344</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>243</v>
+        <v>345</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>244</v>
+        <v>345</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6204,13 +6183,13 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>246</v>
+        <v>343</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
@@ -6219,19 +6198,19 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>83</v>
+        <v>348</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>247</v>
+        <v>349</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>248</v>
+        <v>350</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>83</v>
+        <v>351</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -6239,10 +6218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>297</v>
+        <v>352</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>250</v>
+        <v>352</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6265,17 +6244,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>114</v>
+        <v>353</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>251</v>
+        <v>354</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>253</v>
+        <v>356</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6324,7 +6305,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>255</v>
+        <v>352</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6333,7 +6314,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>83</v>
+        <v>357</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6342,27 +6323,27 @@
         <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>83</v>
+        <v>358</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>256</v>
+        <v>359</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>257</v>
+        <v>360</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>83</v>
+        <v>361</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>259</v>
+        <v>362</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6382,20 +6363,22 @@
         <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>260</v>
+        <v>363</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>262</v>
+        <v>365</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6420,13 +6403,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>83</v>
+        <v>366</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>83</v>
+        <v>367</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>83</v>
+        <v>368</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6444,7 +6427,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>263</v>
+        <v>362</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6453,7 +6436,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>83</v>
+        <v>369</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6465,10 +6448,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>264</v>
+        <v>137</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>265</v>
+        <v>370</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6479,21 +6462,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>371</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>267</v>
+        <v>371</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>83</v>
+        <v>372</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>83</v>
@@ -6502,22 +6485,22 @@
         <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>268</v>
+        <v>188</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>269</v>
+        <v>373</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>270</v>
+        <v>373</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>271</v>
+        <v>374</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>272</v>
+        <v>375</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6542,13 +6525,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>83</v>
+        <v>366</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6566,13 +6549,13 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>273</v>
+        <v>371</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
@@ -6584,27 +6567,27 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>275</v>
+        <v>380</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>83</v>
+        <v>381</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>382</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>277</v>
+        <v>382</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6615,7 +6598,7 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>83</v>
@@ -6624,22 +6607,22 @@
         <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>206</v>
+        <v>383</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>278</v>
+        <v>384</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>279</v>
+        <v>384</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>280</v>
+        <v>385</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>281</v>
+        <v>386</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6688,13 +6671,13 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>282</v>
+        <v>382</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>83</v>
@@ -6709,10 +6692,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>283</v>
+        <v>387</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>284</v>
+        <v>388</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6723,18 +6706,18 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>389</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>301</v>
+        <v>389</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>302</v>
+        <v>83</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>94</v>
@@ -6746,23 +6729,21 @@
         <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>390</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>303</v>
+        <v>390</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6786,11 +6767,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y40" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>306</v>
+        <v>394</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6808,10 +6791,10 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>301</v>
+        <v>389</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>94</v>
@@ -6823,30 +6806,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>308</v>
+        <v>395</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>309</v>
+        <v>396</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>310</v>
+        <v>397</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>312</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>399</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>399</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6854,7 +6837,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>94</v>
@@ -6866,22 +6849,22 @@
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>314</v>
+        <v>188</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>315</v>
+        <v>400</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
+        <v>400</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>316</v>
+        <v>401</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>317</v>
+        <v>402</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6906,13 +6889,13 @@
         <v>83</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>83</v>
+        <v>392</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>83</v>
+        <v>403</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>83</v>
+        <v>404</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -6930,7 +6913,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>313</v>
+        <v>399</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6945,19 +6928,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>319</v>
+        <v>405</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>320</v>
+        <v>406</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>321</v>
+        <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -6965,10 +6948,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>322</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>322</v>
+        <v>407</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6979,7 +6962,7 @@
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6988,19 +6971,19 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>323</v>
+        <v>408</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>324</v>
+        <v>409</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>324</v>
+        <v>409</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>325</v>
+        <v>410</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7050,13 +7033,13 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>322</v>
+        <v>407</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
@@ -7068,31 +7051,31 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>83</v>
+        <v>411</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>309</v>
+        <v>412</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>326</v>
+        <v>413</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>321</v>
+        <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>83</v>
+        <v>414</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>327</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>328</v>
+        <v>83</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7108,23 +7091,21 @@
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>329</v>
+        <v>416</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7172,7 +7153,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>327</v>
+        <v>415</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7187,41 +7168,41 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>333</v>
+        <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>334</v>
+        <v>420</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>335</v>
+        <v>421</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>83</v>
+        <v>422</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>337</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>337</v>
+        <v>423</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>338</v>
+        <v>83</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7230,22 +7211,22 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>339</v>
+        <v>424</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>340</v>
+        <v>425</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>340</v>
+        <v>425</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>341</v>
+        <v>426</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>342</v>
+        <v>427</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7294,34 +7275,34 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>337</v>
+        <v>423</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>428</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>343</v>
+        <v>83</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>344</v>
+        <v>429</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>345</v>
+        <v>430</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7329,10 +7310,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7352,20 +7333,18 @@
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>348</v>
+        <v>206</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>349</v>
+        <v>207</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7414,7 +7393,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>347</v>
+        <v>209</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7426,7 +7405,7 @@
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7435,13 +7414,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>352</v>
+        <v>210</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>353</v>
+        <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7449,14 +7428,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>354</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>354</v>
+        <v>432</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7472,23 +7451,21 @@
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>355</v>
+        <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>356</v>
+        <v>141</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>356</v>
+        <v>213</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7536,7 +7513,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>354</v>
+        <v>216</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7548,22 +7525,22 @@
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>359</v>
+        <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>360</v>
+        <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>361</v>
+        <v>210</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>362</v>
+        <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7571,45 +7548,45 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>433</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>433</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>83</v>
+        <v>434</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>364</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>365</v>
+        <v>435</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>365</v>
+        <v>436</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>366</v>
+        <v>143</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>367</v>
+        <v>149</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7658,45 +7635,45 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>363</v>
+        <v>437</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>368</v>
+        <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>369</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>370</v>
+        <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>371</v>
+        <v>137</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>438</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>438</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7719,20 +7696,16 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>188</v>
+        <v>439</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>374</v>
+        <v>440</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7756,13 +7729,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>379</v>
+        <v>83</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7780,7 +7753,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>373</v>
+        <v>438</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7789,7 +7762,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7801,10 +7774,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>137</v>
+        <v>443</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>381</v>
+        <v>444</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7815,21 +7788,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>382</v>
+        <v>445</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>382</v>
+        <v>445</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>83</v>
@@ -7841,20 +7814,16 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>188</v>
+        <v>439</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>384</v>
+        <v>446</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7878,13 +7847,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>387</v>
+        <v>83</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7902,16 +7871,16 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>382</v>
+        <v>445</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -7920,27 +7889,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>391</v>
+        <v>448</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>392</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>393</v>
+        <v>449</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7951,7 +7920,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7963,19 +7932,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>394</v>
+        <v>188</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>395</v>
+        <v>450</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>395</v>
+        <v>451</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>396</v>
+        <v>452</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>397</v>
+        <v>453</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8000,13 +7969,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>83</v>
+        <v>454</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>83</v>
+        <v>455</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8024,13 +7993,13 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>393</v>
+        <v>449</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>83</v>
@@ -8042,13 +8011,13 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>83</v>
+        <v>456</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>398</v>
+        <v>457</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8059,10 +8028,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>400</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>400</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8073,7 +8042,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
@@ -8088,15 +8057,17 @@
         <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>401</v>
+        <v>459</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>401</v>
+        <v>460</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8120,13 +8091,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>404</v>
+        <v>463</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>405</v>
+        <v>464</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8144,13 +8115,13 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>400</v>
+        <v>458</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
@@ -8162,27 +8133,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>406</v>
+        <v>456</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>408</v>
+        <v>380</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>465</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>465</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8205,19 +8176,17 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>188</v>
+        <v>466</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>411</v>
+        <v>467</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>413</v>
+        <v>469</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8242,13 +8211,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>403</v>
+        <v>83</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>414</v>
+        <v>83</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8266,7 +8235,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>410</v>
+        <v>465</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8287,10 +8256,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>416</v>
+        <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>417</v>
+        <v>470</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8301,10 +8270,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>418</v>
+        <v>471</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>418</v>
+        <v>471</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8327,17 +8296,15 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>419</v>
+        <v>206</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>420</v>
+        <v>472</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8386,7 +8353,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>418</v>
+        <v>471</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8404,27 +8371,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>422</v>
+        <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>425</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8435,7 +8402,7 @@
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8444,19 +8411,19 @@
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>427</v>
+        <v>476</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>428</v>
+        <v>477</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>428</v>
+        <v>477</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>429</v>
+        <v>478</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8506,13 +8473,13 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>426</v>
+        <v>475</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
@@ -8524,27 +8491,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>430</v>
+        <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>431</v>
+        <v>479</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>432</v>
+        <v>480</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>433</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8564,23 +8531,21 @@
         <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>435</v>
+        <v>482</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>436</v>
+        <v>483</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>436</v>
+        <v>483</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8628,7 +8593,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>434</v>
+        <v>481</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8640,7 +8605,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>439</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8649,10 +8614,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>440</v>
+        <v>479</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>441</v>
+        <v>485</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8663,10 +8628,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>442</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>442</v>
+        <v>486</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8677,7 +8642,7 @@
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
@@ -8686,19 +8651,23 @@
         <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>206</v>
+        <v>424</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>207</v>
+        <v>487</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8746,19 +8715,19 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>209</v>
+        <v>486</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
@@ -8767,10 +8736,10 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>83</v>
+        <v>490</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>210</v>
+        <v>491</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8781,21 +8750,21 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>443</v>
+        <v>492</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>443</v>
+        <v>492</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
@@ -8807,17 +8776,15 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8866,19 +8833,19 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -8901,14 +8868,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>444</v>
+        <v>493</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>444</v>
+        <v>493</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>445</v>
+        <v>139</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8921,26 +8888,24 @@
         <v>83</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>446</v>
+        <v>141</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>447</v>
+        <v>213</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
@@ -8988,7 +8953,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>448</v>
+        <v>216</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9012,7 +8977,7 @@
         <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>137</v>
+        <v>210</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9023,42 +8988,46 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>494</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>494</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>83</v>
+        <v>434</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>450</v>
+        <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9106,19 +9075,19 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>453</v>
+        <v>83</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>83</v>
@@ -9127,10 +9096,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>454</v>
+        <v>83</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>455</v>
+        <v>137</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9141,10 +9110,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>495</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>495</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9152,7 +9121,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>94</v>
@@ -9164,19 +9133,23 @@
         <v>83</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>450</v>
+        <v>188</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
@@ -9200,13 +9173,11 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9224,16 +9195,16 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>495</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>453</v>
+        <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9242,16 +9213,16 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>83</v>
+        <v>499</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>454</v>
+        <v>298</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>459</v>
+        <v>299</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
@@ -9259,10 +9230,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9282,22 +9253,22 @@
         <v>83</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>188</v>
+        <v>353</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>463</v>
+        <v>503</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>464</v>
+        <v>356</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9322,13 +9293,13 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>465</v>
+        <v>83</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>466</v>
+        <v>83</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9346,7 +9317,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9364,27 +9335,27 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>467</v>
+        <v>504</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>468</v>
+        <v>359</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>391</v>
+        <v>360</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>83</v>
+        <v>361</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>469</v>
+        <v>505</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>469</v>
+        <v>505</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9395,7 +9366,7 @@
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
@@ -9410,16 +9381,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>470</v>
+        <v>506</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>471</v>
+        <v>507</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>472</v>
+        <v>508</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>473</v>
+        <v>365</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9444,13 +9415,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>474</v>
+        <v>367</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>475</v>
+        <v>368</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9468,16 +9439,16 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>469</v>
+        <v>505</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>83</v>
+        <v>369</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9486,13 +9457,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>467</v>
+        <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>468</v>
+        <v>137</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9503,21 +9474,21 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>83</v>
+        <v>372</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>83</v>
@@ -9529,17 +9500,19 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>477</v>
+        <v>188</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>480</v>
+        <v>513</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9564,13 +9537,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>83</v>
+        <v>366</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9588,13 +9561,13 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>83</v>
@@ -9606,27 +9579,27 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>481</v>
+        <v>380</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>83</v>
+        <v>381</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9637,7 +9610,7 @@
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>83</v>
@@ -9649,16 +9622,20 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>206</v>
+        <v>84</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
@@ -9706,13 +9683,13 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>83</v>
@@ -9727,1345 +9704,15 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>485</v>
+        <v>430</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="P70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y71" s="2"/>
-      <c r="Z71" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="P73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP75" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -915,6 +915,42 @@
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationVitalSignsCategory_VS</t>
+  </si>
+  <si>
+    <t>Observation.category:second.id</t>
+  </si>
+  <si>
+    <t>Observation.category:second.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationVitalSignsCategory_CS</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.category:second.text</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1944,10 +1980,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP64"/>
+  <dimension ref="A1:AP75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.54296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -5373,15 +5409,15 @@
         <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
+        <v>205</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>94</v>
@@ -5393,23 +5429,19 @@
         <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>292</v>
+        <v>207</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>83</v>
       </c>
@@ -5433,11 +5465,13 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
@@ -5455,10 +5489,10 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>290</v>
+        <v>209</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>94</v>
@@ -5467,44 +5501,44 @@
         <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>299</v>
+        <v>210</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>212</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>83</v>
@@ -5513,23 +5547,21 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>303</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>304</v>
+        <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>304</v>
+        <v>213</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>83</v>
       </c>
@@ -5565,46 +5597,46 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>216</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>308</v>
+        <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>309</v>
+        <v>210</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>310</v>
+        <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
@@ -5612,10 +5644,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>218</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5638,18 +5670,20 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>312</v>
+        <v>219</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>313</v>
+        <v>220</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>313</v>
+        <v>221</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5697,7 +5731,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>224</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5718,13 +5752,13 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>315</v>
+        <v>226</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>310</v>
+        <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
@@ -5732,14 +5766,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>228</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5755,23 +5789,19 @@
         <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>318</v>
+        <v>206</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>319</v>
+        <v>207</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
@@ -5819,7 +5849,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>209</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5831,22 +5861,22 @@
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>324</v>
+        <v>210</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5854,21 +5884,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>230</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>327</v>
+        <v>139</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5877,23 +5907,21 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>328</v>
+        <v>140</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>329</v>
+        <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>329</v>
+        <v>213</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
@@ -5929,46 +5957,46 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>326</v>
+        <v>216</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>333</v>
+        <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>334</v>
+        <v>210</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>335</v>
+        <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -5976,10 +6004,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>232</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6002,18 +6030,20 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>337</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>233</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>338</v>
+        <v>234</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6022,7 +6052,7 @@
         <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>83</v>
@@ -6061,7 +6091,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>238</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6082,13 +6112,13 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>340</v>
+        <v>239</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>341</v>
+        <v>240</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>342</v>
+        <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
@@ -6096,10 +6126,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>242</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6110,7 +6140,7 @@
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6122,20 +6152,18 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>344</v>
+        <v>206</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>345</v>
+        <v>243</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>345</v>
+        <v>244</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6183,13 +6211,13 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>246</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
@@ -6198,19 +6226,19 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>348</v>
+        <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>349</v>
+        <v>247</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>350</v>
+        <v>248</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -6218,10 +6246,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>352</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>250</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6244,19 +6272,17 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>353</v>
+        <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>354</v>
+        <v>251</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>356</v>
+        <v>253</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6305,7 +6331,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>255</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6314,7 +6340,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>357</v>
+        <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6323,27 +6349,27 @@
         <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>358</v>
+        <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>359</v>
+        <v>256</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>360</v>
+        <v>257</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>361</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>362</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>362</v>
+        <v>259</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6363,22 +6389,20 @@
         <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>363</v>
+        <v>260</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>365</v>
+        <v>262</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6403,13 +6427,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>367</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>368</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6427,7 +6451,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>362</v>
+        <v>263</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6436,7 +6460,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>369</v>
+        <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6448,10 +6472,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>370</v>
+        <v>265</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6462,21 +6486,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>371</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>371</v>
+        <v>267</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>83</v>
@@ -6485,22 +6509,22 @@
         <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>188</v>
+        <v>268</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>373</v>
+        <v>269</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>373</v>
+        <v>270</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>374</v>
+        <v>271</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>375</v>
+        <v>272</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6525,13 +6549,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>376</v>
+        <v>83</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6549,13 +6573,13 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>371</v>
+        <v>273</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
@@ -6567,27 +6591,27 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>380</v>
+        <v>275</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>382</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>382</v>
+        <v>277</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6598,7 +6622,7 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>83</v>
@@ -6607,22 +6631,22 @@
         <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>383</v>
+        <v>206</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>384</v>
+        <v>278</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>384</v>
+        <v>279</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>385</v>
+        <v>280</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>386</v>
+        <v>281</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6671,13 +6695,13 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>382</v>
+        <v>282</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>83</v>
@@ -6692,10 +6716,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>387</v>
+        <v>283</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>388</v>
+        <v>284</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6706,18 +6730,18 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>389</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>389</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>83</v>
+        <v>303</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>94</v>
@@ -6729,21 +6753,23 @@
         <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>390</v>
+        <v>304</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>390</v>
+        <v>304</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6767,13 +6793,11 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>394</v>
+        <v>307</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6791,10 +6815,10 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>389</v>
+        <v>302</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>94</v>
@@ -6806,30 +6830,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>83</v>
+        <v>308</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>395</v>
+        <v>309</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>396</v>
+        <v>310</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>397</v>
+        <v>311</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>83</v>
+        <v>312</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>398</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>399</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>399</v>
+        <v>314</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6837,7 +6861,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>94</v>
@@ -6849,22 +6873,22 @@
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>188</v>
+        <v>315</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>400</v>
+        <v>316</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>400</v>
+        <v>316</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>401</v>
+        <v>317</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>402</v>
+        <v>318</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6889,13 +6913,13 @@
         <v>83</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>403</v>
+        <v>83</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -6913,7 +6937,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>399</v>
+        <v>314</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6928,19 +6952,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>405</v>
+        <v>320</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>406</v>
+        <v>321</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -6948,10 +6972,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>407</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>407</v>
+        <v>323</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6962,7 +6986,7 @@
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6971,19 +6995,19 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>408</v>
+        <v>324</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>409</v>
+        <v>325</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>409</v>
+        <v>325</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>410</v>
+        <v>326</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7033,13 +7057,13 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>407</v>
+        <v>323</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
@@ -7051,31 +7075,31 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>412</v>
+        <v>310</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>413</v>
+        <v>327</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>414</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>415</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>415</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7091,21 +7115,23 @@
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>416</v>
+        <v>330</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>417</v>
+        <v>331</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>417</v>
+        <v>331</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7153,7 +7179,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>415</v>
+        <v>328</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7168,41 +7194,41 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>83</v>
+        <v>334</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>420</v>
+        <v>335</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>421</v>
+        <v>336</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>422</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>423</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>423</v>
+        <v>338</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>339</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7211,22 +7237,22 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>424</v>
+        <v>340</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>425</v>
+        <v>341</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>425</v>
+        <v>341</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>426</v>
+        <v>342</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>427</v>
+        <v>343</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7275,34 +7301,34 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>423</v>
+        <v>338</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>428</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>83</v>
+        <v>344</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>429</v>
+        <v>345</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>430</v>
+        <v>346</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>83</v>
+        <v>347</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7310,10 +7336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>431</v>
+        <v>348</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
+        <v>348</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7333,18 +7359,20 @@
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>206</v>
+        <v>349</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>207</v>
+        <v>350</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7393,7 +7421,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>209</v>
+        <v>348</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7405,7 +7433,7 @@
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7414,13 +7442,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>83</v>
+        <v>352</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>210</v>
+        <v>353</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>83</v>
+        <v>354</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7428,14 +7456,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>432</v>
+        <v>355</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>432</v>
+        <v>355</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7451,21 +7479,23 @@
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>140</v>
+        <v>356</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>141</v>
+        <v>357</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>213</v>
+        <v>357</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7513,7 +7543,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>216</v>
+        <v>355</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7525,22 +7555,22 @@
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>83</v>
+        <v>360</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>83</v>
+        <v>361</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>210</v>
+        <v>362</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>83</v>
+        <v>363</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7548,45 +7578,45 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>433</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>433</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>434</v>
+        <v>83</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>365</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>435</v>
+        <v>366</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>436</v>
+        <v>366</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>143</v>
+        <v>367</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>149</v>
+        <v>368</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7635,45 +7665,45 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>437</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>83</v>
+        <v>369</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>83</v>
+        <v>370</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>137</v>
+        <v>372</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>83</v>
+        <v>373</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>438</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>438</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7696,16 +7726,20 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>439</v>
+        <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>440</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7729,13 +7763,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7753,7 +7787,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>438</v>
+        <v>374</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7762,7 +7796,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>442</v>
+        <v>381</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7774,10 +7808,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>443</v>
+        <v>137</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>444</v>
+        <v>382</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7788,21 +7822,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>445</v>
+        <v>383</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>445</v>
+        <v>383</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>83</v>
+        <v>384</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>83</v>
@@ -7814,16 +7848,20 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>439</v>
+        <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>446</v>
+        <v>385</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7847,13 +7885,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7871,16 +7909,16 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>445</v>
+        <v>383</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>442</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -7889,27 +7927,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>83</v>
+        <v>390</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>443</v>
+        <v>391</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>448</v>
+        <v>392</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>83</v>
+        <v>393</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>449</v>
+        <v>394</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>449</v>
+        <v>394</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7920,7 +7958,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7932,19 +7970,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>188</v>
+        <v>395</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>450</v>
+        <v>396</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>451</v>
+        <v>396</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>452</v>
+        <v>397</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>453</v>
+        <v>398</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7969,13 +8007,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>454</v>
+        <v>83</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>455</v>
+        <v>83</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -7993,13 +8031,13 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>449</v>
+        <v>394</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>83</v>
@@ -8011,13 +8049,13 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>457</v>
+        <v>399</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8028,10 +8066,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>401</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>401</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8042,7 +8080,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
@@ -8057,17 +8095,15 @@
         <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>459</v>
+        <v>402</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>460</v>
+        <v>402</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8091,13 +8127,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>463</v>
+        <v>405</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>464</v>
+        <v>406</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8115,13 +8151,13 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>401</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
@@ -8133,27 +8169,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>456</v>
+        <v>407</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>457</v>
+        <v>408</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>83</v>
+        <v>410</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8176,17 +8212,19 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>466</v>
+        <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>467</v>
+        <v>412</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>469</v>
+        <v>414</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8211,13 +8249,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>83</v>
+        <v>404</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>83</v>
+        <v>416</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8235,7 +8273,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8256,10 +8294,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>83</v>
+        <v>417</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>470</v>
+        <v>418</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8270,10 +8308,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>471</v>
+        <v>419</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>471</v>
+        <v>419</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8296,15 +8334,17 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>206</v>
+        <v>420</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>472</v>
+        <v>421</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8353,7 +8393,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>471</v>
+        <v>419</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8371,27 +8411,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>83</v>
+        <v>423</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>474</v>
+        <v>425</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>83</v>
+        <v>426</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>427</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>427</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8402,7 +8442,7 @@
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8411,19 +8451,19 @@
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>476</v>
+        <v>428</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>477</v>
+        <v>429</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>477</v>
+        <v>429</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>478</v>
+        <v>430</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8473,13 +8513,13 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>427</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
@@ -8491,27 +8531,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>83</v>
+        <v>431</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>479</v>
+        <v>432</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>480</v>
+        <v>433</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>83</v>
+        <v>434</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>481</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>481</v>
+        <v>435</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8531,21 +8571,23 @@
         <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>482</v>
+        <v>436</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>483</v>
+        <v>437</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>483</v>
+        <v>437</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8593,7 +8635,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>481</v>
+        <v>435</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8605,7 +8647,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>106</v>
+        <v>440</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8614,10 +8656,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>479</v>
+        <v>441</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>485</v>
+        <v>442</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8628,10 +8670,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>486</v>
+        <v>443</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>486</v>
+        <v>443</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8642,7 +8684,7 @@
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
@@ -8651,23 +8693,19 @@
         <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>424</v>
+        <v>206</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>487</v>
+        <v>207</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8715,19 +8753,19 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>486</v>
+        <v>209</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
@@ -8736,10 +8774,10 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>490</v>
+        <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>491</v>
+        <v>210</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8750,21 +8788,21 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>492</v>
+        <v>444</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>492</v>
+        <v>444</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
@@ -8776,15 +8814,17 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>206</v>
+        <v>140</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8833,19 +8873,19 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -8868,14 +8908,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>493</v>
+        <v>445</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>493</v>
+        <v>445</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>139</v>
+        <v>446</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8888,24 +8928,26 @@
         <v>83</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>141</v>
+        <v>447</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>213</v>
+        <v>448</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
@@ -8953,7 +8995,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>216</v>
+        <v>449</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8977,7 +9019,7 @@
         <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>210</v>
+        <v>137</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -8988,46 +9030,42 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>494</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>494</v>
+        <v>450</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>434</v>
+        <v>83</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>140</v>
+        <v>451</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9075,19 +9113,19 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>454</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>83</v>
@@ -9096,10 +9134,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>83</v>
+        <v>455</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>137</v>
+        <v>456</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9110,10 +9148,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9121,7 +9159,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>94</v>
@@ -9133,23 +9171,19 @@
         <v>83</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>188</v>
+        <v>451</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>496</v>
+        <v>458</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
@@ -9173,11 +9207,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9195,16 +9231,16 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>495</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>83</v>
+        <v>454</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9213,16 +9249,16 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>499</v>
+        <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>298</v>
+        <v>455</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>299</v>
+        <v>460</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
@@ -9230,10 +9266,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>500</v>
+        <v>461</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>500</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9253,22 +9289,22 @@
         <v>83</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>353</v>
+        <v>188</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>501</v>
+        <v>462</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>502</v>
+        <v>463</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>356</v>
+        <v>465</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9293,13 +9329,13 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>83</v>
+        <v>466</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>83</v>
+        <v>467</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9317,7 +9353,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>500</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9335,27 +9371,27 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>504</v>
+        <v>468</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>359</v>
+        <v>469</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>361</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>505</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>505</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9366,7 +9402,7 @@
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
@@ -9381,16 +9417,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>506</v>
+        <v>471</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>507</v>
+        <v>472</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>508</v>
+        <v>473</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>365</v>
+        <v>474</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9415,13 +9451,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>367</v>
+        <v>475</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>368</v>
+        <v>476</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9439,16 +9475,16 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>505</v>
+        <v>470</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>369</v>
+        <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9457,13 +9493,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>83</v>
+        <v>468</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>137</v>
+        <v>469</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9474,21 +9510,21 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>509</v>
+        <v>477</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>509</v>
+        <v>477</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>83</v>
@@ -9500,19 +9536,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>188</v>
+        <v>478</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>510</v>
+        <v>479</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>513</v>
+        <v>481</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9537,13 +9571,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>376</v>
+        <v>83</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9561,13 +9595,13 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>509</v>
+        <v>477</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>83</v>
@@ -9579,27 +9613,27 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>379</v>
+        <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>380</v>
+        <v>482</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>514</v>
+        <v>483</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>514</v>
+        <v>483</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9610,7 +9644,7 @@
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>83</v>
@@ -9622,20 +9656,16 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
@@ -9683,13 +9713,13 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>514</v>
+        <v>483</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>83</v>
@@ -9704,15 +9734,1345 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>430</v>
+        <v>486</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y71" s="2"/>
+      <c r="Z71" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -1357,7 +1357,7 @@
     <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
   </si>
   <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
+    <t>これは、結果の送信に関与する機器（ゲートウェイなど）を表すことを意図したものではない。そのような機器は、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -648,6 +648,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="vital-signs"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -802,9 +810,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>vital-signs</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -3888,7 +3893,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3907,7 +3912,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3960,10 +3965,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3986,13 +3991,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4043,7 +4048,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4067,7 +4072,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4078,10 +4083,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4110,7 +4115,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4151,10 +4156,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4163,7 +4168,7 @@
         <v>195</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4187,7 +4192,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4198,10 +4203,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4224,19 +4229,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4285,7 +4290,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4306,10 +4311,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4320,10 +4325,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4346,13 +4351,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4403,7 +4408,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4427,7 +4432,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4438,10 +4443,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4470,7 +4475,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4511,10 +4516,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4523,7 +4528,7 @@
         <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4547,7 +4552,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4558,10 +4563,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4587,23 +4592,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4645,7 +4650,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4666,10 +4671,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4680,10 +4685,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4706,16 +4711,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4765,7 +4770,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4786,10 +4791,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4800,10 +4805,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4829,21 +4834,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>254</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4946,7 +4951,7 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>260</v>
@@ -5188,7 +5193,7 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>278</v>
@@ -5409,7 +5414,7 @@
         <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5432,13 +5437,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5489,7 +5494,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5513,7 +5518,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5527,7 +5532,7 @@
         <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5556,7 +5561,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5597,10 +5602,10 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
@@ -5609,7 +5614,7 @@
         <v>195</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5633,7 +5638,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5647,7 +5652,7 @@
         <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5670,19 +5675,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5731,7 +5736,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5752,10 +5757,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5769,7 +5774,7 @@
         <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5792,13 +5797,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5849,7 +5854,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5873,7 +5878,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5887,7 +5892,7 @@
         <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5916,7 +5921,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -5957,10 +5962,10 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
@@ -5969,7 +5974,7 @@
         <v>195</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5993,7 +5998,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6007,7 +6012,7 @@
         <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6033,16 +6038,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6091,7 +6096,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6112,10 +6117,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6129,7 +6134,7 @@
         <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6152,16 +6157,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6211,7 +6216,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6232,10 +6237,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6249,7 +6254,7 @@
         <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6275,14 +6280,14 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6392,7 +6397,7 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>260</v>
@@ -6634,7 +6639,7 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>278</v>
@@ -8696,13 +8701,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8753,7 +8758,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8777,7 +8782,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8820,7 +8825,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -8873,7 +8878,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8897,7 +8902,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9656,7 +9661,7 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>484</v>
@@ -10136,13 +10141,13 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10193,7 +10198,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10217,7 +10222,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10260,7 +10265,7 @@
         <v>141</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>143</v>
@@ -10313,7 +10318,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10337,7 +10342,7 @@
         <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -909,7 +909,7 @@
     <t>second</t>
   </si>
   <si>
-    <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１．バイタルサイン・基本情報、中分類１．バイタルサインの「焦点」</t>
+    <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１、バイタルサイン・基本情報、中分類１、バイタルサインの「焦点」</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -968,7 +968,7 @@
     <t>このObservationの対象を特定するコード</t>
   </si>
   <si>
-    <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１．バイタルサイン・基本情報、中分類１．バイタルサインの「観察名称」</t>
+    <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１、バイタルサイン・基本情報、中分類１、バイタルサインの「観察名称」</t>
   </si>
   <si>
     <t>どのような観察が行われているかを知ることは、観察を理解するために不可欠です。 / Knowing what kind of observation is being made is essential to understanding the observation.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -543,7 +543,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -1033,7 +1033,7 @@
     <t>配偶者、親、胎児、ドナーなど、このObservationのsubject要素が実際の対象でない場合、その実際の対象に関する情報</t>
   </si>
   <si>
-    <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
+    <t>通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1591,7 +1591,7 @@
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
   </si>
   <si>
-    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではない）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
